--- a/instagram-daily-checker/reports/2026-10-11.xlsx
+++ b/instagram-daily-checker/reports/2026-10-11.xlsx
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>取得日時：2026-10-11 08:54:03</t>
+          <t>取得日時：2026-10-11 09:16:01</t>
         </is>
       </c>
     </row>

--- a/instagram-daily-checker/reports/2026-10-11.xlsx
+++ b/instagram-daily-checker/reports/2026-10-11.xlsx
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>取得日時：2026-10-11 09:16:01</t>
+          <t>取得日時：2026-10-11 09:26:04</t>
         </is>
       </c>
     </row>
